--- a/data/macro/USA/US PCE.xlsx
+++ b/data/macro/USA/US PCE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1C3491-8D4F-4FA8-846A-57B7B20029E4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93097390-A1C5-46FD-A17A-C575FE90E079}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" xr2:uid="{930D0BEB-3F5E-4361-8A72-4031355357EE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" activeTab="1" xr2:uid="{930D0BEB-3F5E-4361-8A72-4031355357EE}"/>
   </bookViews>
   <sheets>
     <sheet name="PCECYOY" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <numFmt numFmtId="176" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
     <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="181" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="179" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -200,10 +200,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
@@ -524,14 +524,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA7CE9F8-3779-45AC-AD23-DE117BAEFF9E}">
-  <dimension ref="A1:G674"/>
+  <dimension ref="A1:G675"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.375" style="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.375" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.25" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
@@ -14483,7 +14485,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D643" s="11" t="str">
-        <f t="shared" ref="D643:D674" si="10">IF(
+        <f t="shared" ref="D643:D675" si="10">IF(
 AND(
   B643 &gt;= IF(
          YEAR(B643)&gt;=2007,
@@ -15242,8 +15244,32 @@
         <f t="shared" si="10"/>
         <v>UTC-5</v>
       </c>
+      <c r="E674" s="12">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F674" s="12">
+        <v>2.8000000000000001E-2</v>
+      </c>
       <c r="G674" s="12">
         <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="675" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A675" s="9">
+        <v>46023</v>
+      </c>
+      <c r="B675" s="9">
+        <v>46094</v>
+      </c>
+      <c r="C675" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D675" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="G675" s="12">
+        <v>2.9000000000000001E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/macro/USA/US PCE.xlsx
+++ b/data/macro/USA/US PCE.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93097390-A1C5-46FD-A17A-C575FE90E079}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005D5690-B66D-467C-B7B2-E85D0B763416}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" activeTab="1" xr2:uid="{930D0BEB-3F5E-4361-8A72-4031355357EE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" xr2:uid="{930D0BEB-3F5E-4361-8A72-4031355357EE}"/>
   </bookViews>
   <sheets>
     <sheet name="PCECYOY" sheetId="1" r:id="rId1"/>
     <sheet name="PCESRVY" sheetId="3" r:id="rId2"/>
-    <sheet name="info" sheetId="2" r:id="rId3"/>
+    <sheet name="fig" sheetId="4" r:id="rId3"/>
+    <sheet name="info" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -225,6 +226,4888 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PCECYOY!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Actual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>PCECYOY!$B$2:$B$675</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="674"/>
+                <c:pt idx="0">
+                  <c:v>25569</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25628</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25659</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25689</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25720</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25750</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>25781</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>25812</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>25842</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>25873</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25903</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>25934</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>25965</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>25993</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>26024</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26054</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>26085</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>26115</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>26146</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>26177</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>26207</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26238</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26268</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>26299</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26330</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26359</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>26390</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>26420</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26451</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>26481</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26512</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>26543</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>26573</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>26604</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>26634</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>26665</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>26696</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>26724</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>26755</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>26785</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>26816</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>26846</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>26877</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>26908</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>26938</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>26969</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>26999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>27030</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>27061</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>27089</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>27120</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>27150</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>27181</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>27211</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>27242</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>27273</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>27303</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>27334</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>27364</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>27395</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>27426</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>27454</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>27485</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>27515</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>27546</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>27576</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>27607</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>27638</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>27668</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>27699</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>27729</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>27760</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>27791</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>27820</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>27851</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>27881</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>27912</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>27942</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>27973</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>28004</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>28034</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>28065</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>28095</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>28126</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>28157</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>28185</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>28216</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>28246</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>28277</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>28307</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>28338</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>28369</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>28399</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>28430</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>28460</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>28491</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>28522</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>28550</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>28581</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>28611</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>28642</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>28672</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>28703</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>28734</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>28764</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>28795</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>28825</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>28856</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>28887</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>28915</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>28946</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>28976</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>29007</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>29037</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>29068</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>29099</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>29129</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>29160</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>29190</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>29221</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>29252</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>29281</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>29312</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>29342</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>29373</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>29403</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>29434</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>29465</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>29495</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>29526</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>29556</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>29587</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>29618</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>29646</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>29677</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>29707</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>29738</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>29768</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>29799</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>29830</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>29860</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>29891</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>29921</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>29952</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>29983</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>30011</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>30042</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>30072</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>30103</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>30133</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>30164</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>30195</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>30225</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>30256</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>30286</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>30317</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>30348</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>30376</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>30407</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>30437</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>30468</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>30498</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>30529</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>30560</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>30590</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>30621</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>30651</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>30682</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>30713</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>30742</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>30773</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>30803</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>30834</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>30864</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>30895</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>30926</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>30956</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>30987</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>31017</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>31048</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>31079</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>31107</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>31138</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>31168</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>31199</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>31229</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>31260</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>31291</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>31321</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>31352</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>31382</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>31413</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>31444</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>31472</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>31503</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>31533</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>31564</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>31594</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>31625</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>31656</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>31686</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>31717</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>31747</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>31778</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>31809</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>31837</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>31868</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>31898</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>31929</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>31959</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>31990</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>32021</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>32051</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>32082</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>32112</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>32143</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>32174</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>32203</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>32234</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>32264</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>32295</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>32325</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>32356</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>32387</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>32417</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>32448</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>32478</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>32509</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>32540</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>32568</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>32599</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>32629</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>32660</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>32690</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>32721</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>32752</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>32782</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>32813</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>32843</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>32874</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>32905</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>32933</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>32964</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>32994</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>33025</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>33055</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>33086</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>33117</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>33147</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>33178</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>33208</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>33239</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>33270</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>33298</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>33329</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>33359</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>33390</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>33420</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>33451</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>33482</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>33512</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>33543</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>33573</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>33604</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>33635</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>33664</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>33695</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>33725</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>33756</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>33786</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>33817</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>33848</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>33878</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>33909</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>33939</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>33970</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>34001</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>34029</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>34060</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>34090</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>34121</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>34151</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>34182</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>34213</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>34243</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>34274</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>34304</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>34335</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>34366</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>34394</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>34425</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>34455</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>34486</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>34516</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>34547</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>34578</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>34608</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>34639</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>34669</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>34700</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>34731</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>34759</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>34790</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>34820</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>34851</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>34881</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>34912</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>34943</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>34973</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>35004</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>35034</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>35065</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>35096</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>35125</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>35156</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>35186</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>35217</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>35247</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>35278</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>35309</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>35339</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>35370</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>35400</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>35431</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>35462</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>35490</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>35521</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>35551</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>35582</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>35612</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>35643</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>35674</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>35704</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>35735</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>35765</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>35796</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>35827</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>35855</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>35886</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>35916</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>35947</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>35977</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>36008</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>36039</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>36069</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>36100</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>36130</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>36161</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>36192</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>36220</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>36251</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>36281</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>36312</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>36342</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>36373</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>36404</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>36434</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>36465</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>36495</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>36526</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>36557</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>36586</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>36617</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>36647</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>36678</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>36708</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>36739</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>36770</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>36800</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>36831</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>36861</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>36892</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>36923</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>36951</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>36982</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>37012</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>37043</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>37073</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>37104</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>37135</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>37165</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>37196</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>37226</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>37257</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>37288</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>37316</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>37347</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>37377</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>37408</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>37438</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>37469</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>37500</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>37530</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>37561</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>37591</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>37622</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>37653</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>37681</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>37712</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>37742</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>37773</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>37803</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>37834</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>37865</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>37895</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>37926</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>37956</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>37987</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>38018</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>38047</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>38078</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>38108</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>38139</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>38169</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>38200</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>38231</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>38261</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>38292</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>38322</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>38353</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>38384</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>38412</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>38443</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>38473</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>38504</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>38534</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>38565</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>38596</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>38626</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>38657</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>38687</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>38718</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>38749</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>38777</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>38808</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>38838</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>38869</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>38899</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>38930</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>38961</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>38991</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>39022</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>39052</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>39083</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>39114</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>39142</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>39173</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>39203</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>39234</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>39264</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>39295</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>39326</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>39356</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>39387</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>39417</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>39448</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>39479</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>39508</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>39539</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>39569</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>39600</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>39630</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>39661</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>39692</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>39722</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>39753</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>39783</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>39814</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>39845</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>39873</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>39904</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>39934</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>39965</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>39995</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>40026</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>40057</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>40087</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>40118</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>40148</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>40179</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>40210</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>40238</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>40269</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>40299</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>40330</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>40360</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>40391</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>40422</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>40452</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>40483</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>40513</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>40544</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>40575</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>40603</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>40634</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>40664</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>40695</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>40725</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>40756</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>40787</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>40817</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>40848</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>40878</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>40909</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>40940</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>40969</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>41030</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>41061</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>41091</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>41122</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>41153</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>41183</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>41214</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>41244</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>41275</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>41306</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>41334</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>41365</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>41395</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>41426</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>41456</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>41487</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>41518</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>41548</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>41579</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>41609</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>41640</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>41671</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>41699</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>41730</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>41760</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>41791</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>41821</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>41880</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>41911</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>41943</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>41969</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>41996</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>42037</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>42065</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>42093</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>42124</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>42156</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>42180</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>42219</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>42244</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>42275</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>42307</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>42333</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>42361</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>42401</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>42426</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>42457</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>42489</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>42521</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>42550</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>42584</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>42611</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>42643</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>42674</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>42704</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>42726</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>42765</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>42795</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>42825</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>42856</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>42885</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>42916</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>42948</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>42978</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>43007</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>43038</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>43069</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>43091</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>43129</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>43160</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>43188</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>43220</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>43251</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>43280</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>43312</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>43342</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>43371</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>43402</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>43433</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>43455</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>43525</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>43553</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>43584</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>43584</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>43616</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>43644</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>43676</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>43707</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>43735</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>43769</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>43796</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>43819</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>43861</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>43889</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>43917</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>43951</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>43980</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>44008</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>44043</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>44071</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>44105</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>44134</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>44160</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>44188</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>44225</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>44253</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>44281</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>44316</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>44344</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>44372</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>44407</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>44435</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>44470</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>44498</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>44524</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>44553</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>44589</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>44617</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>44651</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>44680</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>44708</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>44742</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>44771</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>44799</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>44834</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>44862</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>44896</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>44918</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>44953</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>44981</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>45016</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>45044</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>45072</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>45107</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>45135</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>45169</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>45198</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>45226</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>45260</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>45282</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>45317</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>45351</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>45380</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>45408</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>45443</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>45471</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>45499</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>45534</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>45596</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>45623</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>45646</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>45688</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>45716</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>45744</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>45777</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>45807</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>45835</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>45869</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>45898</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>45926</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>45996</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>46094</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PCECYOY!$E$2:$E$675</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="674"/>
+                <c:pt idx="0">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>8.7999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>9.9000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>7.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>9.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>8.7999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>9.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>9.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>8.7999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>8.6999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>8.4000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>7.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5F3D-492E-8C5B-1C1FD655024F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1093353679"/>
+        <c:axId val="1097226431"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1093353679"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+          <c:min val="40179"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1097226431"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1097226431"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="6.0000000000000012E-2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1093353679"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>209549</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51DEC50C-67EA-4E7A-A677-95098A32EB0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15268,6 +20151,12 @@
         <f t="shared" si="10"/>
         <v>UTC-4</v>
       </c>
+      <c r="E675" s="12">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F675" s="12">
+        <v>2.9000000000000001E-2</v>
+      </c>
       <c r="G675" s="12">
         <v>2.9000000000000001E-2</v>
       </c>
@@ -29614,6 +34503,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52162A65-93F6-4405-8109-9016CC8B9DA4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD86A386-B1DD-453E-BAB6-FA78D0F33318}">
   <dimension ref="B2:C3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>

--- a/data/macro/USA/US PCE.xlsx
+++ b/data/macro/USA/US PCE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995A5E36-B2FA-4104-8A5E-E692E9E4E127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023D7426-6D00-4DCF-99FD-9E4EBECBF325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{930D0BEB-3F5E-4361-8A72-4031355357EE}"/>
   </bookViews>
@@ -20202,13 +20202,13 @@
         <v>UTC-4</v>
       </c>
       <c r="E676" s="12">
-        <v>0.03</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="F676" s="12">
-        <v>0.03</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="G676" s="12">
-        <v>3.1E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.4">
@@ -20225,8 +20225,14 @@
         <f t="shared" si="10"/>
         <v>UTC-4</v>
       </c>
+      <c r="E677" s="12">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="F677" s="12">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="G677" s="12">
-        <v>0.03</v>
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
   </sheetData>
